--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -31,13 +31,16 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
+    <t>OID:1.2.250.1.215.300.2 (use: usual, )</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-nabm (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>V94</t>
+    <t>V96</t>
   </si>
   <si>
     <t>Name</t>
@@ -408,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -441,65 +444,67 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>6</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>8</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -523,15 +528,15 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -549,22 +554,28 @@
       <c r="A19" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>33</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -579,250 +590,250 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -837,13 +848,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -851,38 +862,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V96</t>
+    <t>V97</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T00:00:00+00:00</t>
+    <t>2025-06-02T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V97</t>
+    <t>V98</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T00:00:00+00:00</t>
+    <t>2025-06-20T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1043</t>
+    <t>1050</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V98</t>
+    <t>V99</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T00:00:00+00:00</t>
+    <t>2025-09-08T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V99</t>
+    <t>V100</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T00:00:00+00:00</t>
+    <t>2025-12-18T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1050</t>
+    <t>1047</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V100</t>
+    <t>V102</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T00:00:00+00:00</t>
+    <t>2026-02-23T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V102</t>
+    <t>V103</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T00:00:00+00:00</t>
+    <t>2026-04-13T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1047</t>
+    <t>1046</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="89">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V103</t>
+    <t>V104</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T00:00:00+00:00</t>
+    <t>2026-05-26T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,103 +136,106 @@
     <t>http://purl.org/dc/terms/created</t>
   </si>
   <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>modified</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/modified</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/elements/1.1/type</t>
+  </si>
+  <si>
+    <t>Type fonctionnel d'un concept</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>modified</t>
-  </si>
-  <si>
-    <t>http://purl.org/dc/terms/modified</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>http://purl.org/dc/elements/1.1/type</t>
-  </si>
-  <si>
-    <t>Type fonctionnel d'un concept</t>
+    <t>examenSanguin</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#examenSanguin</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>aPourContingenceTechnique</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#aPourContingenceTechnique</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>nombreMaximumParFacturation</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#nombreMaximumParFacturation</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>ententePrealable</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#ententePrealable</t>
+  </si>
+  <si>
+    <t>coeffB</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#coeffB</t>
+  </si>
+  <si>
+    <t>rmo</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#rmo</t>
   </si>
   <si>
     <t>initativeBiologistePossible</t>
   </si>
   <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/initativeBiologistePossible</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>indicationMédicale</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/indicationMédicale</t>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#initativeBiologistePossible</t>
+  </si>
+  <si>
+    <t>indicationMedicale</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#indicationMedicale</t>
   </si>
   <si>
     <t>remboursementTotal</t>
   </si>
   <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/remboursementTotal</t>
-  </si>
-  <si>
-    <t>ententePréalable</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/ententePréalable</t>
-  </si>
-  <si>
-    <t>aPourContingenceTechnique</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/aPourContingenceTechnique</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>coeffB</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/coeffB</t>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#remboursementTotal</t>
   </si>
   <si>
     <t>acteReserve</t>
   </si>
   <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/acteReserve</t>
-  </si>
-  <si>
-    <t>rmo</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/rmo</t>
-  </si>
-  <si>
-    <t>examenSanguin</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/examenSanguin</t>
-  </si>
-  <si>
-    <t>nombreMaximumParFacturation</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/nombreMaximumParFacturation</t>
-  </si>
-  <si>
-    <t>integer</t>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#acteReserve</t>
   </si>
   <si>
     <t>codeIncompatible</t>
   </si>
   <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/codeIncompatible</t>
-  </si>
-  <si>
-    <t>règleApplicable</t>
-  </si>
-  <si>
-    <t>https://www.data.esante.gouv.fr/DGOS/NABM/règleApplicable</t>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#codeIncompatible</t>
+  </si>
+  <si>
+    <t>regleApplicable</t>
+  </si>
+  <si>
+    <t>http://www.data.esante.gouv.fr/dgos/nabm#regleApplicable</t>
   </si>
   <si>
     <t>parent</t>
@@ -637,203 +640,203 @@
         <v>45</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +857,7 @@
         <v>21</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -862,38 +865,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-nabm.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V104</t>
+    <t>V105</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T00:00:00+00:00</t>
+    <t>2026-06-04T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1046</t>
+    <t>1050</t>
   </si>
   <si>
     <t>Code</t>
